--- a/artfynd/A 11086-2024 artfynd.xlsx
+++ b/artfynd/A 11086-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,117 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Utter barmarksinventering RMÖ/GDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123718670</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56330</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100077</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lutra lutra</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Björnsjön (Y88), Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>630782</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6976965</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Y88</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Peter Nilsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Peter Nilsson, Edvin Rapp</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Utter barmarksinventering RMÖ/GDP</t>
         </is>

--- a/artfynd/A 11086-2024 artfynd.xlsx
+++ b/artfynd/A 11086-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>123718670</v>
       </c>
       <c r="B3" t="n">
-        <v>56330</v>
+        <v>56333</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 11086-2024 artfynd.xlsx
+++ b/artfynd/A 11086-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,117 +789,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
-        <is>
-          <t>Utter barmarksinventering RMÖ/GDP</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>123718670</v>
-      </c>
-      <c r="B3" t="n">
-        <v>56333</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>100077</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Utter</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Lutra lutra</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Björnsjön (Y88), Ång</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>630782</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6976965</v>
-      </c>
-      <c r="S3" t="n">
-        <v>100</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Kramfors</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Y88</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Peter Nilsson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Peter Nilsson, Edvin Rapp</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
         <is>
           <t>Utter barmarksinventering RMÖ/GDP</t>
         </is>
